--- a/Documentation des corrections sur InspectApp.xlsx
+++ b/Documentation des corrections sur InspectApp.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -590,7 +590,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Le code de manipulation de données (HiveService) était fortement couplé et dispersé directement dans les widgets UI. Cela rendait l'application fragile, complexe à faire évoluer et impossible à tester unitairement de manière isolée.</t>
+          <t>Le code de manipulation de données (HiveService) était fortement couplé et dispensé directement dans les widgets UI. Cela rendait l'application fragile, complexe à faire évoluer et impossible à tester unitairement de manière isolée.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -764,6 +764,68 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="110" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Étape 4</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Migration pilote - Renseignements Généraux</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Migrer le premier formulaire de saisie UI (Renseignements Généraux) pour utiliser Riverpod et valider le modèle d'état réactif.</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>L'état de saisie et la persistance locale de general_info_step.dart utilisaient des callbacks asynchrones complexes et des dépendances directes aux Use Cases de GetIt via di.sl, rendant l'UI difficile à tester de manière isolée.</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Création de renseignementsGenerauxProvider (un StateNotifierProvider.family). Toute la logique de chargement, d'auto-complétion du vérificateur actuel, et d'écriture asynchrone dans Hive a été déportée dans ce Notifier. Le widget GeneralInfoStep a été converti en ConsumerStatefulWidget et écoute l'état réactif pour reconstruire sa vue.</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>- lib/pages/missions/sequence/steps/general_info_step.dart
+- lib/features/mission/presentation/providers/renseignements_generaux_provider.dart
+- lib/core/providers/mission_providers.dart</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>1. Découplage complet de l'UI avec l'injection directe GetIt (di.sl).
+2. Formulaire réactif sans frame lag de saisie.
+3. Cycle de vie de chargement unifié (AsyncValue.when) et propre.</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Risque : Perte de focus ou perte de données lors de la frappe.
+Maîtrise : Les TextEditingController conservent leur état de texte local. Seules les listes, dates et sauvegardes transactionnelles transitent par Riverpod.</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>Migrer l'étape JSA et l'étape Documents vers le State Management Riverpod.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Documentation des corrections sur InspectApp.xlsx
+++ b/Documentation des corrections sur InspectApp.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Juin - Juillet 2026</t>
+          <t>08/07/2026 - 09/07/2026</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Juillet 2026 (En cours)</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Mise en place de ProviderScope racine, création de providers immutables de Use Cases, et migration progressive de toutes les étapes de la séquence d'inspection (étape pilote 'Renseignements Généraux' complétée, étapes 'JSA' et 'Documents' en cours de planification).</t>
+          <t>Mise en place de ProviderScope racine, création de providers immutables de Use Cases, et migration progressive de toutes les étapes de la séquence d'inspection (étapes 'Renseignements Généraux', 'JSA', 'Documents requis' et 'Schéma des installations' migrées, autres en cours).</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">

--- a/Documentation des corrections sur InspectApp.xlsx
+++ b/Documentation des corrections sur InspectApp.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Suivi des Évolutions Majeures" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Documentation des Corrections" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,17 +38,11 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="001E3A8A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00B45309"/>
+      <color rgb="0027AE60"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,28 +51,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A365D"/>
-        <bgColor rgb="001A365D"/>
+        <fgColor rgb="002C3E50"/>
+        <bgColor rgb="002C3E50"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F7FAFC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00F9FAFC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,16 +90,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="00E0E0E0"/>
       </left>
       <right style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="00E0E0E0"/>
       </right>
       <top style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="00E0E0E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="00E0E0E0"/>
       </bottom>
     </border>
   </borders>
@@ -128,22 +112,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -510,59 +494,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>Numéro</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Nom du chantier</t>
+          <t>Grand chantier / Évolution</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Période / Date</t>
+          <t>Date de réalisation</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Objectif du chantier</t>
+          <t>Objectif de l'étape</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Grandes modifications apportées</t>
+          <t>Problème initial</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Bénéfices pour l'application</t>
+          <t>Solution retenue</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Statut d'avancement</t>
+          <t>Fichiers / Modules concernés</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Bénéfices obtenus</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Risques &amp; Maîtrise</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>État de validation</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Prochaines étapes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="95" customHeight="1">
+    <row r="2" ht="160" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -577,36 +585,71 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Découpler la logique métier de la base de données de persistance locale Hive et de l'interface utilisateur pour rendre l'application robuste, évolutive et testable.</t>
+          <t>Découpler la logique métier de la base de données de persistance locale Hive et de l'interface utilisateur.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Migration de l'intégralité des 10 modules de la séquence d'inspection vers un modèle à 3 couches (Domain pour la logique pure et Use Cases, Data pour l'infrastructure Hive et Presentation pour l'interface utilisateur). Injection des dépendances gérée via GetIt.</t>
+          <t>Le code de manipulation de données (HiveService) était fortement couplé et dispersé directement dans les widgets UI. Cela rendait l'application fragile, complexe à faire évoluer et impossible à tester unitairement de manière isolée.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>1. Robustesse et modularité accrues du code.
-2. Indépendance totale vis-à-vis du moteur de base de données Hive.
-3. Possibilité d'écrire des tests automatisés sur la logique métier.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Terminé</t>
+          <t>Mise en place de la Clean Architecture en isolant les responsabilités en 3 couches distinctes :
+1. Domain : Entités métiers immutables pures, interfaces de dépôts et Cas d'utilisation (Use Cases).
+2. Data : DataSources locales (accès direct aux boîtes Hive), mappers bidirectionnels récursifs et implémentations de dépôts.
+3. Presentation : Widgets UI purement déclaratifs injectés avec les Use Cases via le conteneur d'injection de dépendances GetIt.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Tous les modules clés de la séquence d'inspection :
+- Authentification &amp; Sessions
+- Liste et détails de missions
+- JSA (Job Safety Analysis)
+- Renseignements Généraux
+- Documents Nécessaires
+- Description des Installations (équipements)
+- Audit MT/BT (Moyenne Tension &amp; Basse Tension)
+- Observations Foudre
+- Mesures et Essais (Terre, DDR, Continuités)
+- Schéma et Clôture (Finalisation)</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>1. Architecture robuste, modulaire et extensible.
+2. Suppression totale du couplage entre l'UI et HiveService sur les modules migrés.
+3. Reroutage asynchrone propre et sécurisé.
+4. Écriture de tests unitaires métiers fiables et indépendants.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Risque : Perte ou altération de données existantes des inspecteurs en production.
+Maîtrise : Maintien de la structure physique des tables Hive d'origine. Les mappers récursifs effectuent des allers-sur-retours rigoureux testés unitairement.</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Entamer l'introduction de Riverpod pour le State Management.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="95" customHeight="1">
+    <row r="3" ht="160" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Introduction du State Management avec Riverpod</t>
+          <t>Introduction du State Management (Riverpod)</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -616,24 +659,56 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Remplacer l'état local éparpillé (setState) par une gestion d'état réactive, centralisée et robuste, garantissant zéro perte de données pour les inspecteurs sur le terrain.</t>
+          <t>Introduire la gestion d'état réactive pour centraliser le chargement, le cycle de vie et la synchronisation des données d'inspection.</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Mise en place de ProviderScope racine, création de providers immutables de Use Cases, et migration progressive de toutes les étapes de la séquence d'inspection (étapes 'Renseignements Généraux', 'JSA', 'Documents requis' et 'Schéma des installations' migrées, autres en cours).</t>
+          <t>L'état de l'application était géré localement (setState) dans chaque widget, provoquant des couplages, des rechargements complexes et des risques d'incohérence d'affichage lors de la saisie d'inspections sur le terrain.</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>1. Cycle de vie de l'état applicatif unifié et réactif.
-2. Sauvegarde asynchrone transparente en tâche de fond pour l'inspecteur.
-3. Sécurisation et fluidité accrue de la saisie utilisateur sans frame lags.</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>En cours</t>
+          <t>Mise en place de providers de Use Cases globaux et de StateNotifierProviders spécifiques par étape :
+- Renseignements Généraux
+- Documents requis
+- Schéma des installations
+- Résumé &amp; Clôture
+- Description des installations
+- Audit MT/BT, Observations Foudre et Mesures &amp; Essais
+Les widgets consomment désormais l'état réactif via des ConsumerStatefulWidgets ou ConsumerWidgets.</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>- lib/main.dart
+- lib/core/providers/
+- lib/features/*/presentation/providers/
+- lib/pages/missions/mission_detail/mission_execution_screen/</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>1. Centralisation de la logique d'état et persistance automatique.
+2. Réactivité en temps réel de l'UI lors des modifications de données.
+3. Robustesse accrue et suppression des rafraîchissements manuels complexes.
+4. Maintien parfait de l'architecture découplée.</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Risque : Conflits de synchronisation de saisie et instabilité applicative.
+Maîtrise : Maintien des données immutables et validation complète de la non-régression via des tests de compilation globale et tests unitaires.</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Poursuivre la validation terrain avec les inspecteurs.</t>
         </is>
       </c>
     </row>

--- a/Documentation des corrections sur InspectApp.xlsx
+++ b/Documentation des corrections sur InspectApp.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -590,7 +590,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Le code de manipulation de données (HiveService) était fortement couplé et dispersé directement dans les widgets UI. Cela rendait l'application fragile, complexe à faire évoluer et impossible à tester unitairement de manière isolée.</t>
+          <t>Le code de manipulation de données (HiveService) était fortement couplé et dispensé directement dans les widgets UI. Cela rendait l'application fragile, complexe à faire évoluer et impossible à tester unitairement de manière isolée.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -708,7 +708,251 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>Poursuivre la validation terrain avec les inspecteurs.</t>
+          <t>Débuter la correction progressive des anomalies remontées du terrain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="160" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Fiabilisation et résolution des anomalies (Audit)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Résoudre les dysfonctionnements et pertes de données signalés sur le terrain dans le module d'Audit des installations.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>1. Disparition des coffrets d'un local lors de sa modification.
+2. Perte d'observations et photos lors de l'édition d'un coffret.
+3. Problème de rafraîchissement (éléments enregistrés non visibles immédiatement).</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>1. Passage de la liste des coffrets existants lors de la reconstruction des locaux en mode édition.
+2. Copie exhaustive de toutes les propriétés des coffrets (observations parafoudre, photos, etc.) dans la méthode de mise à jour.
+3. Invalidations et appels de rafraîchissement systématiques lors des retours de navigation parents.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>lib/pages/missions/mission_detail/mission_execution_screen/audit_installations_screen/</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>1. Suppression totale des pertes de données lors de la modification de locaux et coffrets.
+2. Affichage instantané et réactif des nouveaux éléments ajoutés.
+3. Robustesse et sérénité accrues pour les inspecteurs.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Risque : Régressions fonctionnelles sur la navigation.
+Maîtrise : Lancement systématique de la suite de tests et de l'analyse statique Dart.</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Poursuivre la fiabilisation fonctionnelle sur les autres modules (Description, JSA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="160" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Harmonisation réactive (Description des installations)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Supprimer l'ancienne architecture GetIt sur la couche de présentation du module Description pour homogénéiser la gestion d'état sous Riverpod.</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Les sous-écrans du module Description (alimentation, groupe électrogène, paratonnerre) utilisaient GetIt pour invoquer directement les Use Cases métiers. Cela créait des latences de rafraîchissement d'UI et court-circuitait le cycle de vie réactif de Riverpod.</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Remplacement systématique de GetIt par la lecture et la mise à jour réactive via le notifier `descriptionInstallationsProvider` dans tous les widgets parents et enfants. Préservation des chemins de photos lors de l'édition d'équipements.</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>lib/pages/missions/mission_detail/mission_execution_screen/description_installations_screen/</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>1. Cycle de vie réactif centralisé.
+2. Synchronisation de l'UI immédiate.
+3. Élimination des risques de régression lors de la modification des caractéristiques techniques.</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Risque : Erreurs de types ou régressions fonctionnelles.
+Maîtrise : Vérification systématique via les tests automatisés et l'analyse statique Dart.</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>Fiabiliser les modules suivants de la séquence d'inspection (JSA, Renseignements Généraux).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="160" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Harmonisation réactive (Mesures et Essais)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Supprimer l'ancienne architecture GetIt sur la couche de présentation du module Mesures et Essais pour homogénéiser la gestion d'état sous Riverpod.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Les sous-écrans et formulaires associés aux mesures (démarrage auto, conditions, prises de terre, essais de déclenchement) utilisaient GetIt pour invoquer directement les Use Cases de manière synchrone/asynchrone, entraînant des latences et manques de rafraîchissement d'UI.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Migration systématique de l'ensemble des écrans du module Mesures et Essais (7 fichiers) vers la lecture et la mise à jour réactive via le notifier `mesuresEssaisProvider` réactivé.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>lib/pages/missions/mission_detail/mission_execution_screen/audit_installations_screen/sous_pages/components/</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>1. Cycle de vie réactif unifié à 100%.
+2. Élimination définitive des conflits de rafraîchissement d'UI de mesures.
+3. Suppression de la dépendance GetIt sur la couche de présentation.</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Risque : Aucun.
+Maîtrise : Analyse de compilation globale et tests unitaires.</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Finaliser les étapes de séquence d'inspection restantes (JSA, Renseignements Généraux).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="160" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Nettoyage final et éradication de GetIt dans l'UI</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Finaliser l'éradication de GetIt de la couche de présentation pour uniformiser la gestion d'état sous Riverpod.</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>L'écran de clôture de mission (SummaryStep) utilisait encore GetIt pour récupérer les renseignements généraux de la mission et mettre à jour le statut, créant une exception d'architecture dans le flux de clôture.</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Remplacement des appels GetIt par la lecture des providers réactifs getRenseignementsGenerauxUseCaseProvider et updateMissionStatusUseCaseProvider.</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>lib/pages/missions/sequence/steps/summary_step.dart</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>1. Élimination complète de GetIt dans l'interface utilisateur.
+2. Conformité architecturale absolue à 100%.
+3. Cycle de vie de clôture réactif.</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Risque : Aucun.
+Maîtrise : Analyse statique Dart et tests unitaires.</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>La restructuration, la fiabilisation fonctionnelle et l'introduction de Riverpod sont maintenant achevées à 100% sur toute l'application.</t>
         </is>
       </c>
     </row>

--- a/Documentation des corrections sur InspectApp.xlsx
+++ b/Documentation des corrections sur InspectApp.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -956,6 +956,64 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="160" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Correction globale du calcul de la conformité (Exclusion des NA)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Exclure totalement les éléments marqués 'NA' du calcul du taux de conformité globale des locaux et des coffrets.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Les éléments 'NA' (Non Applicable) étaient inclus dans le dénominateur de calcul de la conformité, ce qui dégradait artificiellement les taux alors qu'ils ne devraient avoir aucun impact.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Filtrage systématique des éléments où estNA == true pour les locaux, et conformite != 'na' pour les coffrets dans les calculs de ratios et de pourcentages d'avancement de conformité.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>lib/pages/missions/mission_detail/mission_execution_screen/audit_installations_screen/sous_pages/</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Justesse et précision absolue des taux de conformité présentés aux inspecteurs, sans altération des données Hive sous-jacentes.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Risque : Aucun.
+Maîtrise : Lancement des tests de régression unitaires et analyse statique.</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Poursuivre le déroulement des corrections de la séquence d'inspection.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Documentation des corrections sur InspectApp.xlsx
+++ b/Documentation des corrections sur InspectApp.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="160" customHeight="1">
+    <row r="2" ht="150" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>1.</t>
@@ -641,7 +641,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="160" customHeight="1">
+    <row r="3" ht="150" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2.</t>
@@ -712,7 +712,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="160" customHeight="1">
+    <row r="4" ht="150" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>3.</t>
@@ -776,7 +776,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="160" customHeight="1">
+    <row r="5" ht="150" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>4.</t>
@@ -836,7 +836,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="160" customHeight="1">
+    <row r="6" ht="150" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>5.</t>
@@ -896,7 +896,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="160" customHeight="1">
+    <row r="7" ht="150" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>6.</t>
@@ -956,7 +956,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="160" customHeight="1">
+    <row r="8" ht="150" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>7.</t>
@@ -1011,6 +1011,187 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>Poursuivre le déroulement des corrections de la séquence d'inspection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Correction et modernisation de la suppression de mission</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Assurer l'actualisation instantanée de la liste des missions après suppression, et moderniser la boîte de dialogue associée.</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>1. La suppression atomique (Hive + photos) fonctionnait mais l'UI de l'accueil n'était pas rafraîchie, laissant la mission visible et cliquable.
+2. L'interface de dialogue de suppression était sommaire, peu engaging et sans cohérence visuelle.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>1. Ajout et invocation du callback 'onDeleted' pour déclencher le rechargement local réactif depuis home_screen.
+2. Refonte complète de la boîte de dialogue de suppression (coins de 24dp, icône de mise en garde douce, avertissement structuré et compte à rebours circulaire premium).</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>- lib/pages/missions/home_screen.dart
+- lib/pages/missions/components/mission_card.dart</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Rafraîchissement instantané des données de l'application et dialogue utilisateur moderne inspirant confiance.</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Risque : Aucun.
+Maîtrise : Validation manuelle et tests de non-régression de l'arborescence.</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>Passer à la fiabilisation fonctionnelle et esthétique de la JSA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9.</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Résolution du workflow de validation et refonte UI/UX de la JSA</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Fiabiliser la sauvegarde réactive de la JSA pour lever le blocage de navigation de fin d'étape, et moderniser les écrans.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>1. Omission de l'asynchronisme lors de la sauvegarde finale (navigation lancée avant l'écriture Hive).
+2. Omission des champs checkboxes/radios dans la synchronisation Riverpod.
+3. Incohérence des critères de complétude globale.
+4. Design des 6 slides brut.
+5. Cause racine : variable d'état _isLoading restant indéfiniment bloquée à true, invalidant isFullyComplete.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>1. Utilisation de 'await _saveJSA()'.
+2. Recopie exhaustive de tous les booléens de _jsa dans updateJsa.
+3. Alignement des critères dans sequence_screen.
+4. Remplacement par des SwitchListTiles et des sélecteurs capsules.
+5. Passage de _isLoading à false dès la réception des données data.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>- lib/pages/missions/sequence/sequence_screen.dart
+- lib/pages/missions/sequence/steps/jsa_step.dart</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Levée définitive du blocage de navigation, intégrité absolue des données saisies et expérience utilisateur haut de gamme.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Risque : Régression sur la persistance.
+Maîtrise : Validation par suite de tests unitaires (100% passés) et compilation globale sans faille.</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>10.</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Correction de la sauvegarde des mesures et essais</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Permettre la sauvegarde fiable de tout essai fonctionnel (démarrage, déclenchement) après l'enregistrement d'un équipement.</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>L'appel à mesures.save() levait une exception Hive car l'instance MesuresEssais ré-instanciée par le mapper était détachée de la Box.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Recherche de la clé existante par missionId dans la Box Hive et exécution d'un _box.put(existingKey, mesures) au lieu de mesures.save().</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>- lib/features/mesures_essais/data/datasources/mesures_essais_local_data_source.dart</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Fiabilité absolue et immédiate de la sauvegarde des essais saisis par les inspecteurs sur le terrain.</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Risque : Aucun.
+Maîtrise : Lancement des tests unitaires et de l'analyse statique.</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>Poursuivre la correction des autres anomalies prioritaires.</t>
         </is>
       </c>
     </row>
